--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:16</t>
+    <t xml:space="preserve">2026-09-09 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:11</t>
+    <t xml:space="preserve">2026-09-17 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:07</t>
+    <t xml:space="preserve">2026-09-23 12:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:36</t>
+    <t xml:space="preserve">2026-10-02 14:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:44</t>
+    <t xml:space="preserve">2026-10-05 10:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -917,7 +917,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>182762.62</v>
+        <v>182762.63</v>
       </c>
     </row>
     <row r="23">
